--- a/research/traditional_assets/database/data/japan/japan_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/japan/japan_investments_asset_management.xlsx
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0137</v>
+        <v>-0.00425</v>
       </c>
       <c r="E2">
-        <v>-0.06964999999999999</v>
+        <v>-0.091</v>
       </c>
       <c r="G2">
-        <v>0.2124868590117977</v>
+        <v>0.4795100104441415</v>
       </c>
       <c r="H2">
-        <v>0.2124868590117977</v>
+        <v>0.4795100104441415</v>
       </c>
       <c r="I2">
-        <v>0.3189530526138706</v>
+        <v>0.1903443280448722</v>
       </c>
       <c r="J2">
-        <v>0.2703745629773126</v>
+        <v>0.1599333415314254</v>
       </c>
       <c r="K2">
-        <v>458.041</v>
+        <v>71.98299999999999</v>
       </c>
       <c r="L2">
-        <v>0.5350321224156056</v>
+        <v>0.1274238374254306</v>
       </c>
       <c r="M2">
-        <v>371.8716</v>
+        <v>159.13201</v>
       </c>
       <c r="N2">
-        <v>0.109602876595243</v>
+        <v>0.06294280911320306</v>
       </c>
       <c r="O2">
-        <v>0.8118740462098372</v>
+        <v>2.210688773738244</v>
       </c>
       <c r="P2">
-        <v>55.7116</v>
+        <v>48.49101</v>
       </c>
       <c r="Q2">
-        <v>0.01642005364142769</v>
+        <v>0.0191800530021359</v>
       </c>
       <c r="R2">
-        <v>0.121630159745525</v>
+        <v>0.6736453051414918</v>
       </c>
       <c r="S2">
-        <v>316.16</v>
+        <v>110.641</v>
       </c>
       <c r="T2">
-        <v>0.8501859243889557</v>
+        <v>0.6952780901843697</v>
       </c>
       <c r="U2">
-        <v>1033.8</v>
+        <v>606.7429999999999</v>
       </c>
       <c r="V2">
-        <v>0.3046950985882284</v>
+        <v>0.2399901115418084</v>
       </c>
       <c r="W2">
-        <v>0.05977715687610741</v>
+        <v>0.05714285714285715</v>
       </c>
       <c r="X2">
-        <v>0.0516121943328221</v>
+        <v>0.08254701612728058</v>
       </c>
       <c r="Y2">
-        <v>0.008164962543285303</v>
+        <v>-0.02540415898442343</v>
       </c>
       <c r="Z2">
-        <v>0.3534285957386713</v>
+        <v>0.2425830828728842</v>
       </c>
       <c r="AA2">
-        <v>0.06407390092545706</v>
+        <v>0.0222974602901061</v>
       </c>
       <c r="AB2">
-        <v>0.04879040247579028</v>
+        <v>0.07938024802941726</v>
       </c>
       <c r="AC2">
-        <v>0.01729788978504128</v>
+        <v>-0.05492325102110898</v>
       </c>
       <c r="AD2">
-        <v>801.2900000000001</v>
+        <v>594.1799999999999</v>
       </c>
       <c r="AE2">
-        <v>3.951458286326758</v>
+        <v>5.967928220856122</v>
       </c>
       <c r="AF2">
-        <v>805.2414582863267</v>
+        <v>600.1479282208561</v>
       </c>
       <c r="AG2">
-        <v>-228.5585417136732</v>
+        <v>-6.595071779143836</v>
       </c>
       <c r="AH2">
-        <v>0.1918090341374596</v>
+        <v>0.1918418097958082</v>
       </c>
       <c r="AI2">
-        <v>0.2387073672332576</v>
+        <v>0.237574340566641</v>
       </c>
       <c r="AJ2">
-        <v>-0.07222941794576455</v>
+        <v>-0.002615426272900353</v>
       </c>
       <c r="AK2">
-        <v>-0.09769373434445926</v>
+        <v>-0.003435998148268261</v>
       </c>
       <c r="AL2">
-        <v>8.109999999999999</v>
+        <v>6.829</v>
       </c>
       <c r="AM2">
-        <v>-4.595000000000001</v>
+        <v>-4.912</v>
       </c>
       <c r="AN2">
-        <v>2.743664633916679</v>
+        <v>5.577688495043556</v>
       </c>
       <c r="AO2">
-        <v>33.54266337854501</v>
+        <v>15.63244984624396</v>
       </c>
       <c r="AP2">
-        <v>-0.7825980452512514</v>
+        <v>-0.06190927999346497</v>
       </c>
       <c r="AQ2">
-        <v>-59.20152339499455</v>
+        <v>-21.73330618892508</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Renewable Japan Energy Infrastructure Fund,Inc. (TSE:9283)</t>
+          <t>Mercuria Holdings Co., Ltd. (TSE:7347)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,91 +722,94 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.7806122448979592</v>
+        <v>0.4514285714285715</v>
       </c>
       <c r="H3">
-        <v>0.7806122448979592</v>
+        <v>0.4514285714285715</v>
       </c>
       <c r="I3">
-        <v>0.358843537414966</v>
+        <v>0.4228571428571429</v>
       </c>
       <c r="J3">
-        <v>0.3564710181593299</v>
+        <v>0.3248656971770744</v>
       </c>
       <c r="K3">
-        <v>1.21</v>
+        <v>11.8</v>
       </c>
       <c r="L3">
-        <v>0.2057823129251701</v>
+        <v>0.3371428571428572</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>2.829</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.03164429530201342</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.2397457627118644</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>2.829</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.03164429530201342</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.2397457627118644</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>0</v>
+        <v>25.3</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>0.2829977628635347</v>
       </c>
       <c r="X3">
-        <v>0.04887865283753826</v>
+        <v>0.08173335771380763</v>
       </c>
       <c r="AB3">
-        <v>0.04887865283753826</v>
+        <v>0.0790108706653852</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>-18.55</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.07020280811232449</v>
+      </c>
+      <c r="AI3">
+        <v>0.05100113335851908</v>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>-0.2618207480592801</v>
+      </c>
+      <c r="AK3">
+        <v>-0.1732835123773938</v>
       </c>
       <c r="AL3">
-        <v>-0.32</v>
+        <v>0.055</v>
       </c>
       <c r="AM3">
-        <v>-0.32</v>
-      </c>
-      <c r="AN3">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="AO3">
-        <v>-6.593749999999999</v>
-      </c>
-      <c r="AP3">
-        <v>0</v>
+        <v>269.0909090909091</v>
       </c>
       <c r="AQ3">
-        <v>-6.593749999999999</v>
+        <v>740.0000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -826,109 +829,115 @@
         </is>
       </c>
       <c r="G4">
-        <v>0.1222222222222222</v>
+        <v>0.1551851851851852</v>
       </c>
       <c r="H4">
-        <v>0.1222222222222222</v>
+        <v>0.1551851851851852</v>
       </c>
       <c r="I4">
-        <v>0.1173616064616133</v>
+        <v>0.1550050467720098</v>
       </c>
       <c r="J4">
-        <v>0.0783434807531712</v>
+        <v>0.1044802629147349</v>
       </c>
       <c r="K4">
-        <v>2.55</v>
+        <v>3.35</v>
       </c>
       <c r="L4">
-        <v>0.08585858585858586</v>
+        <v>0.1240740740740741</v>
       </c>
       <c r="M4">
-        <v>0.2403</v>
+        <v>1.19041</v>
       </c>
       <c r="N4">
-        <v>0.007677316293929712</v>
+        <v>0.03036760204081632</v>
       </c>
       <c r="O4">
-        <v>0.09423529411764706</v>
+        <v>0.3553462686567164</v>
       </c>
       <c r="P4">
-        <v>0.2403</v>
+        <v>0.58941</v>
       </c>
       <c r="Q4">
-        <v>0.007677316293929712</v>
+        <v>0.0150359693877551</v>
       </c>
       <c r="R4">
-        <v>0.09423529411764706</v>
+        <v>0.1759432835820895</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>0.601</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>0.5048680706647289</v>
       </c>
       <c r="U4">
-        <v>20.1</v>
+        <v>15.1</v>
       </c>
       <c r="V4">
-        <v>0.6421725239616614</v>
+        <v>0.385204081632653</v>
+      </c>
+      <c r="W4">
+        <v>0.1278625954198473</v>
       </c>
       <c r="X4">
-        <v>0.05095776112205967</v>
+        <v>0.079419458435975</v>
+      </c>
+      <c r="Y4">
+        <v>0.04844313698387234</v>
       </c>
       <c r="Z4">
-        <v>444.6011912279474</v>
+        <v>3.047638419796483</v>
       </c>
       <c r="AA4">
-        <v>34.83160486780369</v>
+        <v>0.3184180633693839</v>
       </c>
       <c r="AB4">
-        <v>0.04889708668431244</v>
+        <v>0.07938106733024478</v>
       </c>
       <c r="AC4">
-        <v>34.78270778111938</v>
+        <v>0.2390369960391392</v>
       </c>
       <c r="AD4">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AE4">
-        <v>0.06680144045042107</v>
+        <v>0.04931868577868373</v>
       </c>
       <c r="AF4">
-        <v>2.776801440450421</v>
+        <v>0.04931868577868373</v>
       </c>
       <c r="AG4">
-        <v>-17.32319855954958</v>
+        <v>-15.05068131422132</v>
       </c>
       <c r="AH4">
-        <v>0.08148656338250851</v>
+        <v>0.001256548837790489</v>
       </c>
       <c r="AI4">
-        <v>0.09582843179420489</v>
+        <v>0.00218714749061522</v>
       </c>
       <c r="AJ4">
-        <v>-1.239425102614273</v>
+        <v>-0.6232342001053853</v>
       </c>
       <c r="AK4">
-        <v>-1.951513580174278</v>
+        <v>-2.02041044947563</v>
       </c>
       <c r="AL4">
-        <v>0.07199999999999999</v>
+        <v>0.021</v>
       </c>
       <c r="AM4">
-        <v>-0.009000000000000008</v>
+        <v>-0.111</v>
       </c>
       <c r="AN4">
-        <v>0.7406395189942607</v>
+        <v>0</v>
       </c>
       <c r="AO4">
-        <v>48.19444444444445</v>
+        <v>198.5714285714286</v>
       </c>
       <c r="AP4">
-        <v>-4.734407914607702</v>
+        <v>-3.487991034581996</v>
       </c>
       <c r="AQ4">
-        <v>-385.5555555555553</v>
+        <v>-37.56756756756756</v>
       </c>
     </row>
     <row r="5">
@@ -939,7 +948,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>WealthNavi Inc. (TSE:7342)</t>
+          <t>SPARX Group Co., Ltd. (TSE:8739)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -947,101 +956,122 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D5">
+        <v>0.0641</v>
+      </c>
+      <c r="E5">
+        <v>0.0443</v>
+      </c>
       <c r="G5">
-        <v>0</v>
+        <v>0.567287784679089</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>0.567287784679089</v>
       </c>
       <c r="I5">
-        <v>0.01483940532250272</v>
+        <v>0.4503105590062112</v>
       </c>
       <c r="J5">
-        <v>0.01483940532250272</v>
+        <v>0.2800832707665006</v>
       </c>
       <c r="K5">
-        <v>-4.55</v>
+        <v>28.4</v>
       </c>
       <c r="L5">
-        <v>-0.1288951841359773</v>
+        <v>0.2939958592132505</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>22.3985</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.04428331356267299</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>0.7886795774647887</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>16.5585</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.03273724792408066</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>0.5830457746478873</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>5.84</v>
+      </c>
+      <c r="T5">
+        <v>0.2607317454293814</v>
       </c>
       <c r="U5">
-        <v>84.90000000000001</v>
+        <v>125.5</v>
       </c>
       <c r="V5">
-        <v>0.1028218481288604</v>
+        <v>0.2481217872676947</v>
+      </c>
+      <c r="W5">
+        <v>0.1388074291300098</v>
       </c>
       <c r="X5">
-        <v>0.04915100922083437</v>
+        <v>0.08336067454075352</v>
+      </c>
+      <c r="Y5">
+        <v>0.05544675458925624</v>
       </c>
       <c r="Z5">
-        <v>56.40374569347553</v>
+        <v>0.6410086264100862</v>
       </c>
       <c r="AA5">
-        <v>0.8369980440528505</v>
+        <v>0.1795357926744788</v>
       </c>
       <c r="AB5">
-        <v>0.0488812516376238</v>
+        <v>0.07878435432845664</v>
       </c>
       <c r="AC5">
-        <v>0.7881167924152267</v>
+        <v>0.1007514383460222</v>
       </c>
       <c r="AD5">
-        <v>8.970000000000001</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="AE5">
-        <v>0.6258449605782707</v>
+        <v>0</v>
       </c>
       <c r="AF5">
-        <v>9.595844960578271</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="AG5">
-        <v>-75.30415503942173</v>
+        <v>-60.90000000000001</v>
       </c>
       <c r="AH5">
-        <v>0.01148795964743623</v>
+        <v>0.1132538569424965</v>
       </c>
       <c r="AI5">
-        <v>0.1276113722188897</v>
+        <v>0.2795326698398961</v>
       </c>
       <c r="AJ5">
-        <v>-0.1003525746379603</v>
+        <v>-0.1368846931894808</v>
       </c>
       <c r="AK5">
-        <v>7.75999092486769</v>
+        <v>-0.5767045454545455</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>0.601</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>-2.679</v>
       </c>
       <c r="AN5">
-        <v>13.82126348228043</v>
+        <v>1.445190156599552</v>
+      </c>
+      <c r="AO5">
+        <v>72.37936772046589</v>
       </c>
       <c r="AP5">
-        <v>-116.031055530696</v>
+        <v>-1.36241610738255</v>
+      </c>
+      <c r="AQ5">
+        <v>-16.23740201567749</v>
       </c>
     </row>
     <row r="6">
@@ -1052,7 +1082,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SPARX Group Co., Ltd. (TSE:8739)</t>
+          <t>Fund Creation Group Company Limited (TSE:3266)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1061,121 +1091,121 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.127</v>
+        <v>0.06509999999999999</v>
       </c>
       <c r="E6">
-        <v>0.198</v>
+        <v>0.00115</v>
       </c>
       <c r="G6">
-        <v>0.4447739065974796</v>
+        <v>0.1222222222222222</v>
       </c>
       <c r="H6">
-        <v>0.4447739065974796</v>
+        <v>0.1222222222222222</v>
       </c>
       <c r="I6">
-        <v>0.4722016308376575</v>
+        <v>0.09012345679012346</v>
       </c>
       <c r="J6">
-        <v>0.2963737065094891</v>
+        <v>0.0847702589807853</v>
       </c>
       <c r="K6">
-        <v>38.6</v>
+        <v>1.26</v>
       </c>
       <c r="L6">
-        <v>0.2861378799110452</v>
+        <v>0.07777777777777778</v>
       </c>
       <c r="M6">
-        <v>22.0006</v>
+        <v>0.2639</v>
       </c>
       <c r="N6">
-        <v>0.04248860563924295</v>
+        <v>0.01113502109704641</v>
       </c>
       <c r="O6">
-        <v>0.5699637305699481</v>
+        <v>0.2094444444444445</v>
       </c>
       <c r="P6">
-        <v>19.7406</v>
+        <v>0.2639</v>
       </c>
       <c r="Q6">
-        <v>0.03812398609501739</v>
+        <v>0.01113502109704641</v>
       </c>
       <c r="R6">
-        <v>0.5114145077720207</v>
+        <v>0.2094444444444445</v>
       </c>
       <c r="S6">
-        <v>2.259999999999998</v>
+        <v>0</v>
       </c>
       <c r="T6">
-        <v>0.1027244711507867</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>134.6</v>
+        <v>2.76</v>
       </c>
       <c r="V6">
-        <v>0.2599459250675937</v>
+        <v>0.1164556962025316</v>
       </c>
       <c r="W6">
-        <v>0.2017773131207527</v>
+        <v>0.06086956521739131</v>
       </c>
       <c r="X6">
-        <v>0.05253113504617442</v>
+        <v>0.09318780583993291</v>
       </c>
       <c r="Y6">
-        <v>0.1492461780745783</v>
+        <v>-0.03231824062254161</v>
       </c>
       <c r="Z6">
-        <v>0.9705035971223021</v>
+        <v>0.7089715536105032</v>
       </c>
       <c r="AA6">
-        <v>0.2876317482599286</v>
+        <v>0.06009970220957207</v>
       </c>
       <c r="AB6">
-        <v>0.04819213758739659</v>
+        <v>0.07776485209139404</v>
       </c>
       <c r="AC6">
-        <v>0.239439610672532</v>
+        <v>-0.01766514988182197</v>
       </c>
       <c r="AD6">
-        <v>80.7</v>
+        <v>10.5</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>80.7</v>
+        <v>10.5</v>
       </c>
       <c r="AG6">
-        <v>-53.89999999999999</v>
+        <v>7.74</v>
       </c>
       <c r="AH6">
-        <v>0.1348370927318296</v>
+        <v>0.3070175438596491</v>
       </c>
       <c r="AI6">
-        <v>0.2828601472134595</v>
+        <v>0.3790613718411552</v>
       </c>
       <c r="AJ6">
-        <v>-0.116188833800388</v>
+        <v>0.2461832061068703</v>
       </c>
       <c r="AK6">
-        <v>-0.3576642335766423</v>
+        <v>0.3103448275862069</v>
       </c>
       <c r="AL6">
-        <v>0.583</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="AM6">
-        <v>0.2509999999999999</v>
+        <v>0.043</v>
       </c>
       <c r="AN6">
-        <v>1.226443768996961</v>
+        <v>6.862745098039215</v>
       </c>
       <c r="AO6">
-        <v>109.26243567753</v>
+        <v>20.27777777777778</v>
       </c>
       <c r="AP6">
-        <v>-0.8191489361702127</v>
+        <v>5.058823529411764</v>
       </c>
       <c r="AQ6">
-        <v>253.784860557769</v>
+        <v>33.95348837209303</v>
       </c>
     </row>
     <row r="7">
@@ -1186,7 +1216,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Future Venture Capital Co., Ltd. (JASDAQ:8462)</t>
+          <t>Future Venture Capital Co., Ltd. (TSE:8462)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1195,73 +1225,76 @@
         </is>
       </c>
       <c r="D7">
-        <v>-0.009469999999999999</v>
+        <v>-0.00425</v>
       </c>
       <c r="G7">
-        <v>-0.01779788838612368</v>
+        <v>0.1450777202072539</v>
       </c>
       <c r="H7">
-        <v>-0.01779788838612368</v>
+        <v>0.1450777202072539</v>
       </c>
       <c r="I7">
-        <v>0.2594268476621418</v>
+        <v>0.07875647668393783</v>
       </c>
       <c r="J7">
-        <v>0.2594268476621418</v>
+        <v>0.0633049464833175</v>
       </c>
       <c r="K7">
-        <v>2.56</v>
+        <v>2.32</v>
       </c>
       <c r="L7">
-        <v>0.3861236802413273</v>
+        <v>0.6010362694300518</v>
       </c>
       <c r="M7">
-        <v>-0</v>
+        <v>0.1869</v>
       </c>
       <c r="N7">
-        <v>-0</v>
+        <v>0.004944444444444445</v>
       </c>
       <c r="O7">
-        <v>-0</v>
+        <v>0.08056034482758621</v>
       </c>
       <c r="P7">
-        <v>-0</v>
+        <v>0.1869</v>
       </c>
       <c r="Q7">
-        <v>-0</v>
+        <v>0.004944444444444445</v>
       </c>
       <c r="R7">
-        <v>-0</v>
+        <v>0.08056034482758621</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
       <c r="U7">
-        <v>16.8</v>
+        <v>17.2</v>
       </c>
       <c r="V7">
-        <v>0.3387096774193549</v>
+        <v>0.4550264550264551</v>
       </c>
       <c r="W7">
-        <v>0.1103448275862069</v>
+        <v>0.09508196721311475</v>
       </c>
       <c r="X7">
-        <v>0.04887865283753826</v>
+        <v>0.07938024802941726</v>
       </c>
       <c r="Y7">
-        <v>0.06146617474866865</v>
+        <v>0.01570171918369749</v>
       </c>
       <c r="Z7">
-        <v>0.9338028169014088</v>
+        <v>0.5078947368421054</v>
       </c>
       <c r="AA7">
-        <v>0.2422535211267606</v>
+        <v>0.0321522491349481</v>
       </c>
       <c r="AB7">
-        <v>0.04887865283753826</v>
+        <v>0.07938024802941726</v>
       </c>
       <c r="AC7">
-        <v>0.1933748682892224</v>
+        <v>-0.04722799889446916</v>
       </c>
       <c r="AD7">
         <v>0</v>
@@ -1273,7 +1306,7 @@
         <v>0</v>
       </c>
       <c r="AG7">
-        <v>-16.8</v>
+        <v>-17.2</v>
       </c>
       <c r="AH7">
         <v>0</v>
@@ -1282,25 +1315,25 @@
         <v>0</v>
       </c>
       <c r="AJ7">
-        <v>-0.5121951219512195</v>
+        <v>-0.8349514563106797</v>
       </c>
       <c r="AK7">
-        <v>-2.181818181818182</v>
+        <v>-4.410256410256408</v>
       </c>
       <c r="AL7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>-0.362</v>
+        <v>-0.445</v>
       </c>
       <c r="AN7">
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>-9.710982658959539</v>
+        <v>-53.58255451713395</v>
       </c>
       <c r="AQ7">
-        <v>-4.751381215469613</v>
+        <v>-0.6831460674157304</v>
       </c>
     </row>
     <row r="8">
@@ -1311,7 +1344,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JAFCO Group Co., Ltd. (TSE:8595)</t>
+          <t>First Brothers Co.,Ltd. (TSE:3454)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1320,121 +1353,121 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.0137</v>
+        <v>0.0852</v>
       </c>
       <c r="E8">
-        <v>0.349</v>
+        <v>-0.02</v>
       </c>
       <c r="G8">
-        <v>0.3037417461482025</v>
+        <v>0.3250319284802043</v>
       </c>
       <c r="H8">
-        <v>0.3037417461482025</v>
+        <v>0.3250319284802043</v>
       </c>
       <c r="I8">
-        <v>0.6342626559060894</v>
+        <v>0.1533728812616725</v>
       </c>
       <c r="J8">
-        <v>0.448055139695822</v>
+        <v>0.09957559143841581</v>
       </c>
       <c r="K8">
-        <v>418.2</v>
+        <v>12.8</v>
       </c>
       <c r="L8">
-        <v>1.534115920763023</v>
+        <v>0.08173690932311622</v>
       </c>
       <c r="M8">
-        <v>345.892</v>
+        <v>2.73</v>
       </c>
       <c r="N8">
-        <v>0.2331279908337265</v>
+        <v>0.02929184549356223</v>
       </c>
       <c r="O8">
-        <v>0.8270970827355333</v>
+        <v>0.21328125</v>
       </c>
       <c r="P8">
-        <v>31.992</v>
+        <v>2.73</v>
       </c>
       <c r="Q8">
-        <v>0.02156231044011593</v>
+        <v>0.02929184549356223</v>
       </c>
       <c r="R8">
-        <v>0.07649928263988523</v>
+        <v>0.21328125</v>
       </c>
       <c r="S8">
-        <v>313.9</v>
+        <v>0</v>
       </c>
       <c r="T8">
-        <v>0.9075087021382396</v>
+        <v>0</v>
       </c>
       <c r="U8">
-        <v>613.4</v>
+        <v>55.9</v>
       </c>
       <c r="V8">
-        <v>0.4134258947226528</v>
+        <v>0.5997854077253219</v>
       </c>
       <c r="W8">
-        <v>0.2095190380761523</v>
+        <v>0.07142857142857144</v>
       </c>
       <c r="X8">
-        <v>0.04890692659673233</v>
+        <v>0.2212838622614144</v>
       </c>
       <c r="Y8">
-        <v>0.16061211147942</v>
+        <v>-0.1498552908328429</v>
       </c>
       <c r="Z8">
-        <v>0.2005443978518355</v>
+        <v>0.2485875930893198</v>
       </c>
       <c r="AA8">
-        <v>0.08985494819471866</v>
+        <v>0.02475325660612127</v>
       </c>
       <c r="AB8">
-        <v>0.04887251770276574</v>
+        <v>0.0750661565300613</v>
       </c>
       <c r="AC8">
-        <v>0.04098243049195292</v>
+        <v>-0.05031289992394003</v>
       </c>
       <c r="AD8">
-        <v>1.79</v>
+        <v>420.2</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>4.159033972110425</v>
       </c>
       <c r="AF8">
-        <v>1.79</v>
+        <v>424.3590339721104</v>
       </c>
       <c r="AG8">
-        <v>-611.61</v>
+        <v>368.4590339721104</v>
       </c>
       <c r="AH8">
-        <v>0.001204989599391447</v>
+        <v>0.819923923876436</v>
       </c>
       <c r="AI8">
-        <v>0.0009575828255647867</v>
+        <v>0.7346185362221802</v>
       </c>
       <c r="AJ8">
-        <v>-0.7013152312261349</v>
+        <v>0.7981194060081356</v>
       </c>
       <c r="AK8">
-        <v>-0.4869932876286936</v>
+        <v>0.7061862085397176</v>
       </c>
       <c r="AL8">
-        <v>0.008999999999999999</v>
+        <v>4.08</v>
       </c>
       <c r="AM8">
-        <v>-11.391</v>
+        <v>4.073</v>
       </c>
       <c r="AN8">
-        <v>0.01024613623354322</v>
+        <v>13.40350877192983</v>
       </c>
       <c r="AO8">
-        <v>19211.11111111111</v>
+        <v>5.735294117647058</v>
       </c>
       <c r="AP8">
-        <v>-3.500915855752719</v>
+        <v>11.75307923356014</v>
       </c>
       <c r="AQ8">
-        <v>-15.1786498112545</v>
+        <v>5.745150994353056</v>
       </c>
     </row>
     <row r="9">
@@ -1445,7 +1478,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>First Brothers Co.,Ltd. (TSE:3454)</t>
+          <t>JAFCO Group Co., Ltd. (TSE:8595)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1454,121 +1487,118 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.136</v>
+        <v>-0.154</v>
       </c>
       <c r="E9">
-        <v>0.0757</v>
+        <v>-0.272</v>
       </c>
       <c r="G9">
-        <v>0.1611082606464854</v>
+        <v>1.388943731490622</v>
       </c>
       <c r="H9">
-        <v>0.1611082606464854</v>
+        <v>1.388943731490622</v>
       </c>
       <c r="I9">
-        <v>0.1734942097008034</v>
+        <v>0.2566633761105627</v>
       </c>
       <c r="J9">
-        <v>0.1175142434771988</v>
+        <v>0.2459915831038603</v>
       </c>
       <c r="K9">
-        <v>18.9</v>
+        <v>36.4</v>
       </c>
       <c r="L9">
-        <v>0.09697280656747048</v>
+        <v>0.3593287265547878</v>
       </c>
       <c r="M9">
-        <v>3.052</v>
+        <v>129.2624</v>
       </c>
       <c r="N9">
-        <v>0.02720142602495544</v>
+        <v>0.1065290918081424</v>
       </c>
       <c r="O9">
-        <v>0.1614814814814815</v>
+        <v>3.551164835164835</v>
       </c>
       <c r="P9">
-        <v>3.052</v>
+        <v>25.0624</v>
       </c>
       <c r="Q9">
-        <v>0.02720142602495544</v>
+        <v>0.02065468930278556</v>
       </c>
       <c r="R9">
-        <v>0.1614814814814815</v>
+        <v>0.6885274725274726</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>104.2</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>0.8061122182475338</v>
       </c>
       <c r="U9">
-        <v>80.5</v>
+        <v>300.9</v>
       </c>
       <c r="V9">
-        <v>0.7174688057040998</v>
+        <v>0.2479808801714191</v>
       </c>
       <c r="W9">
-        <v>0.1113730111962286</v>
+        <v>0.0194912985274431</v>
       </c>
       <c r="X9">
-        <v>0.1591670780547396</v>
+        <v>0.07940978525956362</v>
       </c>
       <c r="Y9">
-        <v>-0.04779406685851098</v>
+        <v>-0.05991848673212051</v>
       </c>
       <c r="Z9">
-        <v>0.3258571261076568</v>
+        <v>0.0806599304079179</v>
       </c>
       <c r="AA9">
-        <v>0.03829285365619546</v>
+        <v>0.01984166397409092</v>
       </c>
       <c r="AB9">
-        <v>0.04467950457806583</v>
+        <v>0.07937526609236886</v>
       </c>
       <c r="AC9">
-        <v>-0.006386650921870365</v>
+        <v>-0.05953360211827793</v>
       </c>
       <c r="AD9">
-        <v>527.1</v>
+        <v>1.15</v>
       </c>
       <c r="AE9">
-        <v>0.9148926465671056</v>
+        <v>0</v>
       </c>
       <c r="AF9">
-        <v>528.0148926465671</v>
+        <v>1.15</v>
       </c>
       <c r="AG9">
-        <v>447.5148926465671</v>
+        <v>-299.75</v>
       </c>
       <c r="AH9">
-        <v>0.8247463448777652</v>
+        <v>0.0009468527438145813</v>
       </c>
       <c r="AI9">
-        <v>0.7455574545649546</v>
+        <v>0.000880719892781926</v>
       </c>
       <c r="AJ9">
-        <v>0.7995407992996733</v>
+        <v>-0.32807968040278</v>
       </c>
       <c r="AK9">
-        <v>0.712926995820918</v>
+        <v>-0.2983032293377121</v>
       </c>
       <c r="AL9">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="AM9">
-        <v>3.971</v>
+        <v>-7.62</v>
       </c>
       <c r="AN9">
-        <v>12.55089649260661</v>
-      </c>
-      <c r="AO9">
-        <v>8.391959798994975</v>
+        <v>0.04181818181818182</v>
       </c>
       <c r="AP9">
-        <v>10.65587762570105</v>
+        <v>-10.9</v>
       </c>
       <c r="AQ9">
-        <v>8.410979602115336</v>
+        <v>-3.412073490813648</v>
       </c>
     </row>
     <row r="10">
@@ -1579,7 +1609,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ASTMAX Co., Ltd. (JASDAQ:7162)</t>
+          <t>ASTMAX Co., Ltd. (TSE:7162)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1588,46 +1618,46 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.314</v>
+        <v>0.285</v>
       </c>
       <c r="E10">
-        <v>-0.215</v>
+        <v>-0.162</v>
       </c>
       <c r="G10">
-        <v>0.04548581255374032</v>
+        <v>0.06701030927835051</v>
       </c>
       <c r="H10">
-        <v>0.04548581255374032</v>
+        <v>0.06701030927835051</v>
       </c>
       <c r="I10">
-        <v>0.01170435212600007</v>
+        <v>0.01536169987017111</v>
       </c>
       <c r="J10">
-        <v>0.005852176063000034</v>
+        <v>0.010305950545811</v>
       </c>
       <c r="K10">
-        <v>0.466</v>
+        <v>2.58</v>
       </c>
       <c r="L10">
-        <v>0.004006878761822872</v>
+        <v>0.0265979381443299</v>
       </c>
       <c r="M10">
-        <v>0.3483</v>
+        <v>0.2709</v>
       </c>
       <c r="N10">
-        <v>0.01445228215767635</v>
+        <v>0.01157692307692308</v>
       </c>
       <c r="O10">
-        <v>0.7474248927038626</v>
+        <v>0.105</v>
       </c>
       <c r="P10">
-        <v>0.3483</v>
+        <v>0.2709</v>
       </c>
       <c r="Q10">
-        <v>0.01445228215767635</v>
+        <v>0.01157692307692308</v>
       </c>
       <c r="R10">
-        <v>0.7474248927038626</v>
+        <v>0.105</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -1636,73 +1666,73 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>25.6</v>
+        <v>28.2</v>
       </c>
       <c r="V10">
-        <v>1.062240663900415</v>
+        <v>1.205128205128205</v>
       </c>
       <c r="W10">
-        <v>0.009209486166007905</v>
+        <v>0.05341614906832299</v>
       </c>
       <c r="X10">
-        <v>0.08247029130991732</v>
+        <v>0.112090276102194</v>
       </c>
       <c r="Y10">
-        <v>-0.07326080514390941</v>
+        <v>-0.05867412703387104</v>
       </c>
       <c r="Z10">
-        <v>1.634714551074183</v>
+        <v>1.711978938003194</v>
       </c>
       <c r="AA10">
-        <v>0.009566637365634179</v>
+        <v>0.01764357027053095</v>
       </c>
       <c r="AB10">
-        <v>0.0477667732215938</v>
+        <v>0.07971414274583008</v>
       </c>
       <c r="AC10">
-        <v>-0.03820013585595963</v>
+        <v>-0.06207057247529913</v>
       </c>
       <c r="AD10">
-        <v>32.2</v>
+        <v>22.8</v>
       </c>
       <c r="AE10">
-        <v>2.343919238730961</v>
+        <v>1.759575562967014</v>
       </c>
       <c r="AF10">
-        <v>34.54391923873096</v>
+        <v>24.55957556296702</v>
       </c>
       <c r="AG10">
-        <v>8.943919238730963</v>
+        <v>-3.640424437032983</v>
       </c>
       <c r="AH10">
-        <v>0.5890452017387794</v>
+        <v>0.5120890932556793</v>
       </c>
       <c r="AI10">
-        <v>0.3927948576519392</v>
+        <v>0.3613850639813322</v>
       </c>
       <c r="AJ10">
-        <v>0.2706676279564243</v>
+        <v>-0.184235963238795</v>
       </c>
       <c r="AK10">
-        <v>0.1434609717827073</v>
+        <v>-0.09156094816122129</v>
       </c>
       <c r="AL10">
-        <v>0.538</v>
+        <v>0.394</v>
       </c>
       <c r="AM10">
-        <v>0.502</v>
+        <v>0.394</v>
       </c>
       <c r="AN10">
-        <v>6.95464362850972</v>
+        <v>6.209150326797386</v>
       </c>
       <c r="AO10">
-        <v>2.397769516728625</v>
+        <v>3.426395939086294</v>
       </c>
       <c r="AP10">
-        <v>1.931732017004528</v>
+        <v>-0.9914009904773919</v>
       </c>
       <c r="AQ10">
-        <v>2.569721115537849</v>
+        <v>3.426395939086294</v>
       </c>
     </row>
     <row r="11">
@@ -1713,7 +1743,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Fund Creation Group Company Limited (JASDAQ:3266)</t>
+          <t>Japan Asia Investment Co., Ltd. (TSE:8518)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1722,121 +1752,118 @@
         </is>
       </c>
       <c r="D11">
-        <v>-0.2</v>
+        <v>-0.159</v>
       </c>
       <c r="E11">
-        <v>-0.433</v>
+        <v>-0.281</v>
       </c>
       <c r="G11">
-        <v>0.05163120567375887</v>
+        <v>-0.0719298245614035</v>
       </c>
       <c r="H11">
-        <v>0.05163120567375887</v>
+        <v>-0.0719298245614035</v>
       </c>
       <c r="I11">
-        <v>0.0174468085106383</v>
+        <v>-0.09473684210526316</v>
       </c>
       <c r="J11">
-        <v>0.0174468085106383</v>
+        <v>-0.09431444854173651</v>
       </c>
       <c r="K11">
-        <v>0.155</v>
+        <v>-0.007</v>
       </c>
       <c r="L11">
-        <v>0.01099290780141844</v>
+        <v>-0.0003070175438596491</v>
       </c>
       <c r="M11">
-        <v>0.3384</v>
+        <v>-0</v>
       </c>
       <c r="N11">
-        <v>0.01175</v>
+        <v>-0</v>
       </c>
       <c r="O11">
-        <v>2.183225806451613</v>
+        <v>0</v>
       </c>
       <c r="P11">
-        <v>0.3384</v>
+        <v>-0</v>
       </c>
       <c r="Q11">
-        <v>0.01175</v>
+        <v>-0</v>
       </c>
       <c r="R11">
-        <v>2.183225806451613</v>
+        <v>0</v>
       </c>
       <c r="S11">
         <v>0</v>
       </c>
-      <c r="T11">
-        <v>0</v>
-      </c>
       <c r="U11">
-        <v>5.36</v>
+        <v>26.7</v>
       </c>
       <c r="V11">
-        <v>0.1861111111111111</v>
+        <v>0.8870431893687707</v>
       </c>
       <c r="W11">
-        <v>0.007209302325581395</v>
+        <v>-0.0001168614357262104</v>
       </c>
       <c r="X11">
-        <v>0.05498981868245205</v>
+        <v>0.1458531210273985</v>
       </c>
       <c r="Y11">
-        <v>-0.04778051635687065</v>
+        <v>-0.1459699824631247</v>
       </c>
       <c r="Z11">
-        <v>0.5269058295964126</v>
+        <v>0.1609033168666196</v>
       </c>
       <c r="AA11">
-        <v>0.009192825112107623</v>
+        <v>-0.01517550759881152</v>
       </c>
       <c r="AB11">
-        <v>0.04782558949006416</v>
+        <v>0.07982415028931596</v>
       </c>
       <c r="AC11">
-        <v>-0.03863276437795654</v>
+        <v>-0.09499965788812748</v>
       </c>
       <c r="AD11">
-        <v>7.51</v>
+        <v>64.2</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>7.51</v>
+        <v>64.2</v>
       </c>
       <c r="AG11">
-        <v>2.149999999999999</v>
+        <v>37.5</v>
       </c>
       <c r="AH11">
-        <v>0.2068300743596805</v>
+        <v>0.6808059384941675</v>
       </c>
       <c r="AI11">
-        <v>0.2662176533144275</v>
+        <v>0.5408593091828138</v>
       </c>
       <c r="AJ11">
-        <v>0.06946688206785136</v>
+        <v>0.5547337278106509</v>
       </c>
       <c r="AK11">
-        <v>0.09409190371991245</v>
+        <v>0.4076086956521739</v>
       </c>
       <c r="AL11">
-        <v>0.264</v>
+        <v>1.53</v>
       </c>
       <c r="AM11">
-        <v>0.228</v>
+        <v>1.489</v>
       </c>
       <c r="AN11">
-        <v>25.98615916955017</v>
+        <v>-36.47727272727273</v>
       </c>
       <c r="AO11">
-        <v>0.9318181818181818</v>
+        <v>-1.411764705882353</v>
       </c>
       <c r="AP11">
-        <v>7.439446366782006</v>
+        <v>-21.30681818181818</v>
       </c>
       <c r="AQ11">
-        <v>1.078947368421053</v>
+        <v>-1.45063801208865</v>
       </c>
     </row>
     <row r="12">
@@ -1856,25 +1883,25 @@
         </is>
       </c>
       <c r="D12">
-        <v>-0.102</v>
+        <v>-0.139</v>
       </c>
       <c r="G12">
-        <v>-0.2336448598130841</v>
+        <v>0.17825311942959</v>
       </c>
       <c r="H12">
-        <v>-0.2336448598130841</v>
+        <v>0.17825311942959</v>
       </c>
       <c r="I12">
-        <v>-0.004205607476635514</v>
+        <v>-0.3244206773618538</v>
       </c>
       <c r="J12">
-        <v>-0.004205607476635514</v>
+        <v>-0.3244206773618538</v>
       </c>
       <c r="K12">
-        <v>-10.5</v>
+        <v>-16.6</v>
       </c>
       <c r="L12">
-        <v>-0.9813084112149534</v>
+        <v>-2.959001782531194</v>
       </c>
       <c r="M12">
         <v>-0</v>
@@ -1898,73 +1925,73 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>5.93</v>
+        <v>8.81</v>
       </c>
       <c r="V12">
-        <v>0.07293972939729397</v>
+        <v>0.2481690140845071</v>
       </c>
       <c r="W12">
-        <v>-0.8823529411764706</v>
+        <v>-0.4547945205479452</v>
       </c>
       <c r="X12">
-        <v>0.05202069908343809</v>
+        <v>0.07938024802941726</v>
       </c>
       <c r="Y12">
-        <v>-0.9343736402599087</v>
+        <v>-0.5341747685773625</v>
       </c>
       <c r="Z12">
-        <v>0.8505564387917328</v>
+        <v>0.1352785145888594</v>
       </c>
       <c r="AA12">
-        <v>-0.003577106518282989</v>
+        <v>-0.0438871473354232</v>
       </c>
       <c r="AB12">
-        <v>0.04890539678730666</v>
+        <v>0.07938024802941726</v>
       </c>
       <c r="AC12">
-        <v>-0.05248250330558965</v>
+        <v>-0.1232673953648405</v>
       </c>
       <c r="AD12">
-        <v>10.9</v>
+        <v>0</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>10.9</v>
+        <v>0</v>
       </c>
       <c r="AG12">
-        <v>4.970000000000001</v>
+        <v>-8.81</v>
       </c>
       <c r="AH12">
-        <v>0.1182212581344902</v>
+        <v>0</v>
       </c>
       <c r="AI12">
-        <v>0.229957805907173</v>
+        <v>0</v>
       </c>
       <c r="AJ12">
-        <v>0.05760982960472935</v>
+        <v>-0.3300861745972275</v>
       </c>
       <c r="AK12">
-        <v>0.1198456715698095</v>
+        <v>-2.324538258575199</v>
       </c>
       <c r="AL12">
-        <v>0.126</v>
+        <v>0.014</v>
       </c>
       <c r="AM12">
-        <v>0.045</v>
+        <v>-0.076</v>
       </c>
       <c r="AN12">
-        <v>403.7037037037037</v>
+        <v>-0</v>
       </c>
       <c r="AO12">
-        <v>-0.3571428571428572</v>
+        <v>-130</v>
       </c>
       <c r="AP12">
-        <v>184.0740740740741</v>
+        <v>5.438271604938271</v>
       </c>
       <c r="AQ12">
-        <v>-1</v>
+        <v>23.94736842105263</v>
       </c>
     </row>
     <row r="13">
@@ -1975,7 +2002,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Japan Asia Investment Co., Ltd. (TSE:8518)</t>
+          <t>Sun Capital Management Corp. (TSE:2134)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1984,28 +2011,25 @@
         </is>
       </c>
       <c r="D13">
-        <v>-0.0162</v>
-      </c>
-      <c r="E13">
-        <v>-0.305</v>
+        <v>-0.0759</v>
       </c>
       <c r="G13">
-        <v>-0.03858520900321543</v>
+        <v>-1.329931972789116</v>
       </c>
       <c r="H13">
-        <v>-0.03858520900321543</v>
+        <v>-1.329931972789116</v>
       </c>
       <c r="I13">
-        <v>-0.1141479099678456</v>
+        <v>-1.438775510204082</v>
       </c>
       <c r="J13">
-        <v>-0.1141479099678456</v>
+        <v>-1.438775510204082</v>
       </c>
       <c r="K13">
-        <v>-2.47</v>
+        <v>-10.3</v>
       </c>
       <c r="L13">
-        <v>-0.07942122186495178</v>
+        <v>-3.503401360544218</v>
       </c>
       <c r="M13">
         <v>-0</v>
@@ -2029,73 +2053,70 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>45.1</v>
+        <v>0.373</v>
       </c>
       <c r="V13">
-        <v>1.513422818791946</v>
+        <v>0.02702898550724638</v>
       </c>
       <c r="W13">
-        <v>-0.03859375</v>
+        <v>-0.7463768115942029</v>
       </c>
       <c r="X13">
-        <v>0.1486766851556257</v>
+        <v>0.0883685965320722</v>
       </c>
       <c r="Y13">
-        <v>-0.1872704351556257</v>
+        <v>-0.8347454081262751</v>
       </c>
       <c r="Z13">
-        <v>0.1574683544303798</v>
+        <v>0.2254601226993865</v>
       </c>
       <c r="AA13">
-        <v>-0.0179746835443038</v>
+        <v>-0.3243865030674846</v>
       </c>
       <c r="AB13">
-        <v>0.04475546201379339</v>
+        <v>0.07952620180573111</v>
       </c>
       <c r="AC13">
-        <v>-0.06273014555809719</v>
+        <v>-0.4039127048732157</v>
       </c>
       <c r="AD13">
-        <v>126.9</v>
+        <v>3.98</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>126.9</v>
+        <v>3.98</v>
       </c>
       <c r="AG13">
-        <v>81.80000000000001</v>
+        <v>3.607</v>
       </c>
       <c r="AH13">
-        <v>0.8098276962348436</v>
+        <v>0.2238470191226097</v>
       </c>
       <c r="AI13">
-        <v>0.6282178217821782</v>
+        <v>0.4585253456221198</v>
       </c>
       <c r="AJ13">
-        <v>0.7329749103942653</v>
+        <v>0.2072154880220601</v>
       </c>
       <c r="AK13">
-        <v>0.521351179094965</v>
+        <v>0.4342121102684483</v>
       </c>
       <c r="AL13">
-        <v>2.58</v>
+        <v>0.062</v>
       </c>
       <c r="AM13">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AN13">
-        <v>-37.54437869822485</v>
+        <v>-1.14367816091954</v>
       </c>
       <c r="AO13">
-        <v>-1.375968992248062</v>
+        <v>-68.22580645161291</v>
       </c>
       <c r="AP13">
-        <v>-24.20118343195267</v>
-      </c>
-      <c r="AQ13">
-        <v>-1.530172413793103</v>
+        <v>-1.036494252873563</v>
       </c>
     </row>
     <row r="14">
@@ -2106,7 +2127,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sun Capital Management Corp. (JASDAQ:2134)</t>
+          <t>Perfect Solutions Group, Inc. (OTCPK:PSGI)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2114,26 +2135,8 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D14">
-        <v>0.117</v>
-      </c>
-      <c r="G14">
-        <v>-0.6791979949874686</v>
-      </c>
-      <c r="H14">
-        <v>-0.6791979949874686</v>
-      </c>
-      <c r="I14">
-        <v>-0.8045112781954886</v>
-      </c>
-      <c r="J14">
-        <v>-0.8045112781954886</v>
-      </c>
       <c r="K14">
-        <v>-7.08</v>
-      </c>
-      <c r="L14">
-        <v>-1.774436090225564</v>
+        <v>-0.02</v>
       </c>
       <c r="M14">
         <v>-0</v>
@@ -2157,73 +2160,40 @@
         <v>0</v>
       </c>
       <c r="U14">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="V14">
-        <v>0.05968379446640316</v>
-      </c>
-      <c r="W14">
-        <v>-0.6436363636363637</v>
+        <v>0</v>
       </c>
       <c r="X14">
-        <v>0.05120368958220612</v>
-      </c>
-      <c r="Y14">
-        <v>-0.6948400532185698</v>
-      </c>
-      <c r="Z14">
-        <v>0.3958333333333335</v>
-      </c>
-      <c r="AA14">
-        <v>-0.318452380952381</v>
+        <v>0.07938024802941726</v>
       </c>
       <c r="AB14">
-        <v>0.04870828724881481</v>
-      </c>
-      <c r="AC14">
-        <v>-0.3671606682011959</v>
+        <v>0.07938024802941726</v>
       </c>
       <c r="AD14">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="AG14">
-        <v>0.9999999999999998</v>
+        <v>0</v>
       </c>
       <c r="AH14">
-        <v>0.09025530384753684</v>
-      </c>
-      <c r="AI14">
-        <v>0.1538933169834457</v>
+        <v>0</v>
       </c>
       <c r="AJ14">
-        <v>0.03802281368821292</v>
-      </c>
-      <c r="AK14">
-        <v>0.06756756756756754</v>
+        <v>0</v>
       </c>
       <c r="AL14">
-        <v>0.278</v>
+        <v>0</v>
       </c>
       <c r="AM14">
-        <v>0.17</v>
-      </c>
-      <c r="AN14">
-        <v>-0.9507575757575756</v>
-      </c>
-      <c r="AO14">
-        <v>-11.54676258992806</v>
-      </c>
-      <c r="AP14">
-        <v>-0.3787878787878787</v>
-      </c>
-      <c r="AQ14">
-        <v>-18.88235294117647</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/japan/japan_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/japan/japan_investments_asset_management.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ14"/>
+  <dimension ref="A1:AQ16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,121 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.00425</v>
+        <v>-0.0188</v>
       </c>
       <c r="E2">
-        <v>-0.091</v>
+        <v>0.0344</v>
+      </c>
+      <c r="F2">
+        <v>0.5660000000000001</v>
       </c>
       <c r="G2">
-        <v>0.4795100104441415</v>
+        <v>0.1006483313997134</v>
       </c>
       <c r="H2">
-        <v>0.4795100104441415</v>
+        <v>0.1006483313997134</v>
       </c>
       <c r="I2">
-        <v>0.1903443280448722</v>
+        <v>0.1475959303525358</v>
       </c>
       <c r="J2">
-        <v>0.1599333415314254</v>
+        <v>0.1196195630094545</v>
       </c>
       <c r="K2">
-        <v>71.98299999999999</v>
+        <v>382.48</v>
       </c>
       <c r="L2">
-        <v>0.1274238374254306</v>
+        <v>0.5220500921313042</v>
       </c>
       <c r="M2">
-        <v>159.13201</v>
+        <v>373.02641</v>
       </c>
       <c r="N2">
-        <v>0.06294280911320306</v>
+        <v>0.1186470769720102</v>
       </c>
       <c r="O2">
-        <v>2.210688773738244</v>
+        <v>0.9752834396569755</v>
       </c>
       <c r="P2">
-        <v>48.49101</v>
+        <v>80.36341</v>
       </c>
       <c r="Q2">
-        <v>0.0191800530021359</v>
+        <v>0.025560881043257</v>
       </c>
       <c r="R2">
-        <v>0.6736453051414918</v>
+        <v>0.2101114045178833</v>
       </c>
       <c r="S2">
-        <v>110.641</v>
+        <v>292.663</v>
       </c>
       <c r="T2">
-        <v>0.6952780901843697</v>
+        <v>0.7845637524699658</v>
       </c>
       <c r="U2">
-        <v>606.7429999999999</v>
+        <v>908.442</v>
       </c>
       <c r="V2">
-        <v>0.2399901115418084</v>
+        <v>0.2889446564885496</v>
       </c>
       <c r="W2">
-        <v>0.05714285714285715</v>
+        <v>0.1331463521188292</v>
       </c>
       <c r="X2">
-        <v>0.08254701612728058</v>
+        <v>0.06944419070999067</v>
       </c>
       <c r="Y2">
-        <v>-0.02540415898442343</v>
+        <v>0.06370216140883853</v>
       </c>
       <c r="Z2">
-        <v>0.2425830828728842</v>
+        <v>0.3870271889016643</v>
       </c>
       <c r="AA2">
-        <v>0.0222974602901061</v>
+        <v>0.04720910461589681</v>
       </c>
       <c r="AB2">
-        <v>0.07938024802941726</v>
+        <v>0.06714139207934673</v>
       </c>
       <c r="AC2">
-        <v>-0.05492325102110898</v>
+        <v>-0.01590980316764059</v>
       </c>
       <c r="AD2">
-        <v>594.1799999999999</v>
+        <v>750.0700000000001</v>
       </c>
       <c r="AE2">
-        <v>5.967928220856122</v>
+        <v>9.299208136073068</v>
       </c>
       <c r="AF2">
-        <v>600.1479282208561</v>
+        <v>759.3692081360731</v>
       </c>
       <c r="AG2">
-        <v>-6.595071779143836</v>
+        <v>-149.0727918639269</v>
       </c>
       <c r="AH2">
-        <v>0.1918418097958082</v>
+        <v>0.1945419886372176</v>
       </c>
       <c r="AI2">
-        <v>0.237574340566641</v>
+        <v>0.2889676570603328</v>
       </c>
       <c r="AJ2">
-        <v>-0.002615426272900353</v>
+        <v>-0.04977509685676269</v>
       </c>
       <c r="AK2">
-        <v>-0.003435998148268261</v>
+        <v>-0.08669910023439008</v>
       </c>
       <c r="AL2">
-        <v>6.829</v>
+        <v>7.999000000000001</v>
       </c>
       <c r="AM2">
-        <v>-4.912</v>
+        <v>-0.08199999999999896</v>
       </c>
       <c r="AN2">
-        <v>5.577688495043556</v>
+        <v>7.036964067923821</v>
       </c>
       <c r="AO2">
-        <v>15.63244984624396</v>
+        <v>13.22527815976997</v>
       </c>
       <c r="AP2">
-        <v>-0.06190927999346497</v>
+        <v>-1.398562640622262</v>
       </c>
       <c r="AQ2">
-        <v>-21.73330618892508</v>
+        <v>-1290.109756097577</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mercuria Holdings Co., Ltd. (TSE:7347)</t>
+          <t>WealthNavi Inc. (TSE:7342)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,94 +725,97 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.4514285714285715</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>0.4514285714285715</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>0.4228571428571429</v>
+        <v>0.01194608432287576</v>
       </c>
       <c r="J3">
-        <v>0.3248656971770744</v>
+        <v>0.01194608432287576</v>
       </c>
       <c r="K3">
-        <v>11.8</v>
+        <v>3.43</v>
       </c>
       <c r="L3">
-        <v>0.3371428571428572</v>
+        <v>0.06725490196078432</v>
       </c>
       <c r="M3">
-        <v>2.829</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.03164429530201342</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.2397457627118644</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>2.829</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.03164429530201342</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.2397457627118644</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>25.3</v>
+        <v>115</v>
       </c>
       <c r="V3">
-        <v>0.2829977628635347</v>
+        <v>0.1680303915838691</v>
+      </c>
+      <c r="W3">
+        <v>0.04628879892037787</v>
       </c>
       <c r="X3">
-        <v>0.08173335771380763</v>
+        <v>0.06789710465843295</v>
+      </c>
+      <c r="Y3">
+        <v>-0.02160830573805508</v>
       </c>
       <c r="AB3">
-        <v>0.0790108706653852</v>
+        <v>0.06746943558676852</v>
       </c>
       <c r="AD3">
-        <v>6.75</v>
+        <v>10</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>0.8987484976666819</v>
       </c>
       <c r="AF3">
-        <v>6.75</v>
+        <v>10.89874849766668</v>
       </c>
       <c r="AG3">
-        <v>-18.55</v>
+        <v>-104.1012515023333</v>
       </c>
       <c r="AH3">
-        <v>0.07020280811232449</v>
+        <v>0.01567491459062112</v>
       </c>
       <c r="AI3">
-        <v>0.05100113335851908</v>
+        <v>0.1193745662126488</v>
       </c>
       <c r="AJ3">
-        <v>-0.2618207480592801</v>
+        <v>-0.1793925142382965</v>
       </c>
       <c r="AK3">
-        <v>-0.1732835123773938</v>
+        <v>4.392225933389421</v>
       </c>
       <c r="AL3">
-        <v>0.055</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>0.02</v>
-      </c>
-      <c r="AO3">
-        <v>269.0909090909091</v>
-      </c>
-      <c r="AQ3">
-        <v>740.0000000000001</v>
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <v>12.67427122940431</v>
+      </c>
+      <c r="AP3">
+        <v>-131.9407496861005</v>
       </c>
     </row>
     <row r="4">
@@ -820,7 +826,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Broad-minded Co.,Ltd. (TSE:7343)</t>
+          <t>Integral Corporation (TSE:5842)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -828,116 +834,95 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="F4">
+        <v>0.5660000000000001</v>
+      </c>
       <c r="G4">
-        <v>0.1551851851851852</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>0.1551851851851852</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>0.1550050467720098</v>
+        <v>0.5509708737864077</v>
       </c>
       <c r="J4">
-        <v>0.1044802629147349</v>
+        <v>0.3824386065105654</v>
       </c>
       <c r="K4">
-        <v>3.35</v>
+        <v>15.3</v>
       </c>
       <c r="L4">
-        <v>0.1240740740740741</v>
+        <v>0.3713592233009709</v>
       </c>
       <c r="M4">
-        <v>1.19041</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.03036760204081632</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>0.3553462686567164</v>
+        <v>-0</v>
       </c>
       <c r="P4">
-        <v>0.58941</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.0150359693877551</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>0.1759432835820895</v>
+        <v>-0</v>
       </c>
       <c r="S4">
-        <v>0.601</v>
-      </c>
-      <c r="T4">
-        <v>0.5048680706647289</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>15.1</v>
+        <v>102.6</v>
       </c>
       <c r="V4">
-        <v>0.385204081632653</v>
-      </c>
-      <c r="W4">
-        <v>0.1278625954198473</v>
+        <v>0.1641337386018237</v>
       </c>
       <c r="X4">
-        <v>0.079419458435975</v>
-      </c>
-      <c r="Y4">
-        <v>0.04844313698387234</v>
-      </c>
-      <c r="Z4">
-        <v>3.047638419796483</v>
-      </c>
-      <c r="AA4">
-        <v>0.3184180633693839</v>
+        <v>0.06900056073320665</v>
       </c>
       <c r="AB4">
-        <v>0.07938106733024478</v>
-      </c>
-      <c r="AC4">
-        <v>0.2390369960391392</v>
+        <v>0.06723708435671723</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>44.5</v>
       </c>
       <c r="AE4">
-        <v>0.04931868577868373</v>
+        <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.04931868577868373</v>
+        <v>44.5</v>
       </c>
       <c r="AG4">
-        <v>-15.05068131422132</v>
+        <v>-58.09999999999999</v>
       </c>
       <c r="AH4">
-        <v>0.001256548837790489</v>
+        <v>0.06645758661887693</v>
       </c>
       <c r="AI4">
-        <v>0.00218714749061522</v>
+        <v>0.1617593602326427</v>
       </c>
       <c r="AJ4">
-        <v>-0.6232342001053853</v>
+        <v>-0.1024691358024691</v>
       </c>
       <c r="AK4">
-        <v>-2.02041044947563</v>
+        <v>-0.3368115942028985</v>
       </c>
       <c r="AL4">
-        <v>0.021</v>
+        <v>0.675</v>
       </c>
       <c r="AM4">
-        <v>-0.111</v>
-      </c>
-      <c r="AN4">
-        <v>0</v>
+        <v>0.66</v>
       </c>
       <c r="AO4">
-        <v>198.5714285714286</v>
-      </c>
-      <c r="AP4">
-        <v>-3.487991034581996</v>
+        <v>33.62962962962963</v>
       </c>
       <c r="AQ4">
-        <v>-37.56756756756756</v>
+        <v>34.39393939393939</v>
       </c>
     </row>
     <row r="5">
@@ -948,7 +933,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SPARX Group Co., Ltd. (TSE:8739)</t>
+          <t>Rheos Capital Works Inc. (TSE:7330)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -957,121 +942,109 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0641</v>
+        <v>0.202</v>
       </c>
       <c r="E5">
-        <v>0.0443</v>
+        <v>0.0317</v>
       </c>
       <c r="G5">
-        <v>0.567287784679089</v>
+        <v>0.2242090784044017</v>
       </c>
       <c r="H5">
-        <v>0.567287784679089</v>
+        <v>0.2242090784044017</v>
       </c>
       <c r="I5">
-        <v>0.4503105590062112</v>
+        <v>0.1774251315843539</v>
       </c>
       <c r="J5">
-        <v>0.2800832707665006</v>
+        <v>0.1161989181441793</v>
       </c>
       <c r="K5">
-        <v>28.4</v>
+        <v>8.18</v>
       </c>
       <c r="L5">
-        <v>0.2939958592132505</v>
+        <v>0.1125171939477304</v>
       </c>
       <c r="M5">
-        <v>22.3985</v>
+        <v>2.6703</v>
       </c>
       <c r="N5">
-        <v>0.04428331356267299</v>
+        <v>0.02470212765957447</v>
       </c>
       <c r="O5">
-        <v>0.7886795774647887</v>
+        <v>0.3264425427872861</v>
       </c>
       <c r="P5">
-        <v>16.5585</v>
+        <v>2.6703</v>
       </c>
       <c r="Q5">
-        <v>0.03273724792408066</v>
+        <v>0.02470212765957447</v>
       </c>
       <c r="R5">
-        <v>0.5830457746478873</v>
+        <v>0.3264425427872861</v>
       </c>
       <c r="S5">
-        <v>5.84</v>
+        <v>0</v>
       </c>
       <c r="T5">
-        <v>0.2607317454293814</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>125.5</v>
+        <v>20</v>
       </c>
       <c r="V5">
-        <v>0.2481217872676947</v>
-      </c>
-      <c r="W5">
-        <v>0.1388074291300098</v>
+        <v>0.1850138760407031</v>
       </c>
       <c r="X5">
-        <v>0.08336067454075352</v>
-      </c>
-      <c r="Y5">
-        <v>0.05544675458925624</v>
+        <v>0.06804201255997891</v>
       </c>
       <c r="Z5">
-        <v>0.6410086264100862</v>
+        <v>29.01078410912994</v>
       </c>
       <c r="AA5">
-        <v>0.1795357926744788</v>
+        <v>3.371021727995248</v>
       </c>
       <c r="AB5">
-        <v>0.07878435432845664</v>
+        <v>0.0674625266189203</v>
       </c>
       <c r="AC5">
-        <v>0.1007514383460222</v>
+        <v>3.303559201376328</v>
       </c>
       <c r="AD5">
-        <v>64.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>2.505964669087338</v>
       </c>
       <c r="AF5">
-        <v>64.59999999999999</v>
+        <v>2.505964669087338</v>
       </c>
       <c r="AG5">
-        <v>-60.90000000000001</v>
+        <v>-17.49403533091266</v>
       </c>
       <c r="AH5">
-        <v>0.1132538569424965</v>
+        <v>0.02265668652305255</v>
       </c>
       <c r="AI5">
-        <v>0.2795326698398961</v>
+        <v>0.05155673148651844</v>
       </c>
       <c r="AJ5">
-        <v>-0.1368846931894808</v>
+        <v>-0.1930781863512483</v>
       </c>
       <c r="AK5">
-        <v>-0.5767045454545455</v>
+        <v>-0.6115520148781196</v>
       </c>
       <c r="AL5">
-        <v>0.601</v>
+        <v>0</v>
       </c>
       <c r="AM5">
-        <v>-2.679</v>
+        <v>0</v>
       </c>
       <c r="AN5">
-        <v>1.445190156599552</v>
-      </c>
-      <c r="AO5">
-        <v>72.37936772046589</v>
+        <v>0</v>
       </c>
       <c r="AP5">
-        <v>-1.36241610738255</v>
-      </c>
-      <c r="AQ5">
-        <v>-16.23740201567749</v>
+        <v>-0.9939792801654921</v>
       </c>
     </row>
     <row r="6">
@@ -1082,7 +1055,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Fund Creation Group Company Limited (TSE:3266)</t>
+          <t>Broad-minded Co.,Ltd. (TSE:7343)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1090,47 +1063,41 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D6">
-        <v>0.06509999999999999</v>
-      </c>
-      <c r="E6">
-        <v>0.00115</v>
-      </c>
       <c r="G6">
-        <v>0.1222222222222222</v>
+        <v>0.1536741214057508</v>
       </c>
       <c r="H6">
-        <v>0.1222222222222222</v>
+        <v>0.1536741214057508</v>
       </c>
       <c r="I6">
-        <v>0.09012345679012346</v>
+        <v>0.1283456939380352</v>
       </c>
       <c r="J6">
-        <v>0.0847702589807853</v>
+        <v>0.08776801552671261</v>
       </c>
       <c r="K6">
-        <v>1.26</v>
+        <v>2.91</v>
       </c>
       <c r="L6">
-        <v>0.07777777777777778</v>
+        <v>0.09297124600638978</v>
       </c>
       <c r="M6">
-        <v>0.2639</v>
+        <v>0.81291</v>
       </c>
       <c r="N6">
-        <v>0.01113502109704641</v>
+        <v>0.01997321867321867</v>
       </c>
       <c r="O6">
-        <v>0.2094444444444445</v>
+        <v>0.2793505154639175</v>
       </c>
       <c r="P6">
-        <v>0.2639</v>
+        <v>0.81291</v>
       </c>
       <c r="Q6">
-        <v>0.01113502109704641</v>
+        <v>0.01997321867321867</v>
       </c>
       <c r="R6">
-        <v>0.2094444444444445</v>
+        <v>0.2793505154639175</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1139,73 +1106,70 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>2.76</v>
+        <v>12.1</v>
       </c>
       <c r="V6">
-        <v>0.1164556962025316</v>
+        <v>0.2972972972972973</v>
       </c>
       <c r="W6">
-        <v>0.06086956521739131</v>
+        <v>0.1293333333333333</v>
       </c>
       <c r="X6">
-        <v>0.09318780583993291</v>
+        <v>0.06762275289348847</v>
       </c>
       <c r="Y6">
-        <v>-0.03231824062254161</v>
+        <v>0.06171058043984486</v>
       </c>
       <c r="Z6">
-        <v>0.7089715536105032</v>
+        <v>4.190711432103932</v>
       </c>
       <c r="AA6">
-        <v>0.06009970220957207</v>
+        <v>0.3678104260408699</v>
       </c>
       <c r="AB6">
-        <v>0.07776485209139404</v>
+        <v>0.06755509794641934</v>
       </c>
       <c r="AC6">
-        <v>-0.01766514988182197</v>
+        <v>0.3002553280944505</v>
       </c>
       <c r="AD6">
-        <v>10.5</v>
+        <v>0.02</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>0.06889889869748077</v>
       </c>
       <c r="AF6">
-        <v>10.5</v>
+        <v>0.08889889869748077</v>
       </c>
       <c r="AG6">
-        <v>7.74</v>
+        <v>-12.01110110130252</v>
       </c>
       <c r="AH6">
-        <v>0.3070175438596491</v>
+        <v>0.002179487583576805</v>
       </c>
       <c r="AI6">
-        <v>0.3790613718411552</v>
+        <v>0.00366006293938043</v>
       </c>
       <c r="AJ6">
-        <v>0.2461832061068703</v>
+        <v>-0.4186672044721744</v>
       </c>
       <c r="AK6">
-        <v>0.3103448275862069</v>
+        <v>-0.9854131370788577</v>
       </c>
       <c r="AL6">
-        <v>0.07199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AM6">
-        <v>0.043</v>
+        <v>-0.248</v>
       </c>
       <c r="AN6">
-        <v>6.862745098039215</v>
-      </c>
-      <c r="AO6">
-        <v>20.27777777777778</v>
+        <v>0.004772130756382725</v>
       </c>
       <c r="AP6">
-        <v>5.058823529411764</v>
+        <v>-2.865927249177409</v>
       </c>
       <c r="AQ6">
-        <v>33.95348837209303</v>
+        <v>-16.12903225806452</v>
       </c>
     </row>
     <row r="7">
@@ -1216,7 +1180,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Future Venture Capital Co., Ltd. (TSE:8462)</t>
+          <t>SPARX Group Co., Ltd. (TSE:8739)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1225,115 +1189,121 @@
         </is>
       </c>
       <c r="D7">
-        <v>-0.00425</v>
+        <v>0.0199</v>
+      </c>
+      <c r="E7">
+        <v>0.0371</v>
       </c>
       <c r="G7">
-        <v>0.1450777202072539</v>
+        <v>0.4538934426229508</v>
       </c>
       <c r="H7">
-        <v>0.1450777202072539</v>
+        <v>0.4538934426229508</v>
       </c>
       <c r="I7">
-        <v>0.07875647668393783</v>
+        <v>0.4344262295081968</v>
       </c>
       <c r="J7">
-        <v>0.0633049464833175</v>
+        <v>0.305161927695965</v>
       </c>
       <c r="K7">
-        <v>2.32</v>
+        <v>37.3</v>
       </c>
       <c r="L7">
-        <v>0.6010362694300518</v>
+        <v>0.3821721311475409</v>
       </c>
       <c r="M7">
-        <v>0.1869</v>
+        <v>26.1398</v>
       </c>
       <c r="N7">
-        <v>0.004944444444444445</v>
+        <v>0.05732412280701755</v>
       </c>
       <c r="O7">
-        <v>0.08056034482758621</v>
+        <v>0.7007989276139411</v>
       </c>
       <c r="P7">
-        <v>0.1869</v>
+        <v>16.0398</v>
       </c>
       <c r="Q7">
-        <v>0.004944444444444445</v>
+        <v>0.035175</v>
       </c>
       <c r="R7">
-        <v>0.08056034482758621</v>
+        <v>0.4300214477211797</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>10.1</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>0.3863839815147783</v>
       </c>
       <c r="U7">
-        <v>17.2</v>
+        <v>123.9</v>
       </c>
       <c r="V7">
-        <v>0.4550264550264551</v>
+        <v>0.2717105263157895</v>
       </c>
       <c r="W7">
-        <v>0.09508196721311475</v>
+        <v>0.224024024024024</v>
       </c>
       <c r="X7">
-        <v>0.07938024802941726</v>
+        <v>0.07021950879636452</v>
       </c>
       <c r="Y7">
-        <v>0.01570171918369749</v>
+        <v>0.1538045152276595</v>
       </c>
       <c r="Z7">
-        <v>0.5078947368421054</v>
+        <v>0.9242424242424242</v>
       </c>
       <c r="AA7">
-        <v>0.0321522491349481</v>
+        <v>0.28204359984021</v>
       </c>
       <c r="AB7">
-        <v>0.07938024802941726</v>
+        <v>0.06629079015572344</v>
       </c>
       <c r="AC7">
-        <v>-0.04722799889446916</v>
+        <v>0.2157528096844866</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>60.3</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>60.3</v>
       </c>
       <c r="AG7">
-        <v>-17.2</v>
+        <v>-63.60000000000001</v>
       </c>
       <c r="AH7">
-        <v>0</v>
+        <v>0.1167925624636839</v>
       </c>
       <c r="AI7">
-        <v>0</v>
+        <v>0.2397614314115308</v>
       </c>
       <c r="AJ7">
-        <v>-0.8349514563106797</v>
+        <v>-0.1620795107033639</v>
       </c>
       <c r="AK7">
-        <v>-4.410256410256408</v>
+        <v>-0.4984326018808779</v>
       </c>
       <c r="AL7">
-        <v>0</v>
+        <v>0.469</v>
       </c>
       <c r="AM7">
-        <v>-0.445</v>
+        <v>-0.5810000000000001</v>
       </c>
       <c r="AN7">
-        <v>0</v>
+        <v>1.376712328767123</v>
+      </c>
+      <c r="AO7">
+        <v>90.40511727078892</v>
       </c>
       <c r="AP7">
-        <v>-53.58255451713395</v>
+        <v>-1.452054794520548</v>
       </c>
       <c r="AQ7">
-        <v>-0.6831460674157304</v>
+        <v>-72.97762478485369</v>
       </c>
     </row>
     <row r="8">
@@ -1344,7 +1314,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>First Brothers Co.,Ltd. (TSE:3454)</t>
+          <t>Fund Creation Group Company Limited (TSE:3266)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1353,46 +1323,43 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.0852</v>
-      </c>
-      <c r="E8">
-        <v>-0.02</v>
+        <v>0.293</v>
       </c>
       <c r="G8">
-        <v>0.3250319284802043</v>
+        <v>0.07291666666666667</v>
       </c>
       <c r="H8">
-        <v>0.3250319284802043</v>
+        <v>0.07291666666666667</v>
       </c>
       <c r="I8">
-        <v>0.1533728812616725</v>
+        <v>0.1623740946763841</v>
       </c>
       <c r="J8">
-        <v>0.09957559143841581</v>
+        <v>0.1155883385831887</v>
       </c>
       <c r="K8">
-        <v>12.8</v>
+        <v>2.93</v>
       </c>
       <c r="L8">
-        <v>0.08173690932311622</v>
+        <v>0.1017361111111111</v>
       </c>
       <c r="M8">
-        <v>2.73</v>
+        <v>0.2639</v>
       </c>
       <c r="N8">
-        <v>0.02929184549356223</v>
+        <v>0.01178125</v>
       </c>
       <c r="O8">
-        <v>0.21328125</v>
+        <v>0.09006825938566554</v>
       </c>
       <c r="P8">
-        <v>2.73</v>
+        <v>0.2639</v>
       </c>
       <c r="Q8">
-        <v>0.02929184549356223</v>
+        <v>0.01178125</v>
       </c>
       <c r="R8">
-        <v>0.21328125</v>
+        <v>0.09006825938566554</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1401,73 +1368,73 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>55.9</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="V8">
-        <v>0.5997854077253219</v>
+        <v>0.3892857142857143</v>
       </c>
       <c r="W8">
-        <v>0.07142857142857144</v>
+        <v>0.1703488372093023</v>
       </c>
       <c r="X8">
-        <v>0.2212838622614144</v>
+        <v>0.08147858318619644</v>
       </c>
       <c r="Y8">
-        <v>-0.1498552908328429</v>
+        <v>0.08887025402310589</v>
       </c>
       <c r="Z8">
-        <v>0.2485875930893198</v>
+        <v>1.097848392377426</v>
       </c>
       <c r="AA8">
-        <v>0.02475325660612127</v>
+        <v>0.1268984716911312</v>
       </c>
       <c r="AB8">
-        <v>0.0750661565300613</v>
+        <v>0.0630517607705451</v>
       </c>
       <c r="AC8">
-        <v>-0.05031289992394003</v>
+        <v>0.06384671092058615</v>
       </c>
       <c r="AD8">
-        <v>420.2</v>
+        <v>14.3</v>
       </c>
       <c r="AE8">
-        <v>4.159033972110425</v>
+        <v>1.293130366600691</v>
       </c>
       <c r="AF8">
-        <v>424.3590339721104</v>
+        <v>15.59313036660069</v>
       </c>
       <c r="AG8">
-        <v>368.4590339721104</v>
+        <v>6.873130366600691</v>
       </c>
       <c r="AH8">
-        <v>0.819923923876436</v>
+        <v>0.4104197315709586</v>
       </c>
       <c r="AI8">
-        <v>0.7346185362221802</v>
+        <v>0.4494587315076158</v>
       </c>
       <c r="AJ8">
-        <v>0.7981194060081356</v>
+        <v>0.2347931458141088</v>
       </c>
       <c r="AK8">
-        <v>0.7061862085397176</v>
+        <v>0.2646246436062621</v>
       </c>
       <c r="AL8">
-        <v>4.08</v>
+        <v>0.213</v>
       </c>
       <c r="AM8">
-        <v>4.073</v>
+        <v>0.186</v>
       </c>
       <c r="AN8">
-        <v>13.40350877192983</v>
+        <v>2.862862862862863</v>
       </c>
       <c r="AO8">
-        <v>5.735294117647058</v>
+        <v>20.61032863849765</v>
       </c>
       <c r="AP8">
-        <v>11.75307923356014</v>
+        <v>1.376002075395534</v>
       </c>
       <c r="AQ8">
-        <v>5.745150994353056</v>
+        <v>23.60215053763441</v>
       </c>
     </row>
     <row r="9">
@@ -1478,7 +1445,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JAFCO Group Co., Ltd. (TSE:8595)</t>
+          <t>Mercuria Holdings Co., Ltd. (TSE:7347)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1486,119 +1453,116 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D9">
-        <v>-0.154</v>
-      </c>
-      <c r="E9">
-        <v>-0.272</v>
-      </c>
       <c r="G9">
-        <v>1.388943731490622</v>
+        <v>0.4107142857142857</v>
       </c>
       <c r="H9">
-        <v>1.388943731490622</v>
+        <v>0.4107142857142857</v>
       </c>
       <c r="I9">
-        <v>0.2566633761105627</v>
+        <v>0.1816326530612245</v>
       </c>
       <c r="J9">
-        <v>0.2459915831038603</v>
+        <v>0.1419442841403913</v>
       </c>
       <c r="K9">
-        <v>36.4</v>
+        <v>5.62</v>
       </c>
       <c r="L9">
-        <v>0.3593287265547878</v>
+        <v>0.1433673469387755</v>
       </c>
       <c r="M9">
-        <v>129.2624</v>
+        <v>2.5862</v>
       </c>
       <c r="N9">
-        <v>0.1065290918081424</v>
+        <v>0.02691155046826223</v>
       </c>
       <c r="O9">
-        <v>3.551164835164835</v>
+        <v>0.4601779359430606</v>
       </c>
       <c r="P9">
-        <v>25.0624</v>
+        <v>2.5862</v>
       </c>
       <c r="Q9">
-        <v>0.02065468930278556</v>
+        <v>0.02691155046826223</v>
       </c>
       <c r="R9">
-        <v>0.6885274725274726</v>
+        <v>0.4601779359430606</v>
       </c>
       <c r="S9">
-        <v>104.2</v>
+        <v>0</v>
       </c>
       <c r="T9">
-        <v>0.8061122182475338</v>
+        <v>0</v>
       </c>
       <c r="U9">
-        <v>300.9</v>
+        <v>23</v>
       </c>
       <c r="V9">
-        <v>0.2479808801714191</v>
+        <v>0.2393340270551509</v>
       </c>
       <c r="W9">
-        <v>0.0194912985274431</v>
+        <v>0.04722689075630252</v>
       </c>
       <c r="X9">
-        <v>0.07940978525956362</v>
+        <v>0.06757914008240185</v>
       </c>
       <c r="Y9">
-        <v>-0.05991848673212051</v>
+        <v>-0.02035224932609932</v>
       </c>
       <c r="Z9">
-        <v>0.0806599304079179</v>
+        <v>0.3902439024390244</v>
       </c>
       <c r="AA9">
-        <v>0.01984166397409092</v>
+        <v>0.05539289137186004</v>
       </c>
       <c r="AB9">
-        <v>0.07937526609236886</v>
+        <v>0.06757914008240185</v>
       </c>
       <c r="AC9">
-        <v>-0.05953360211827793</v>
+        <v>-0.0121862487105418</v>
       </c>
       <c r="AD9">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AG9">
-        <v>-299.75</v>
+        <v>-23</v>
       </c>
       <c r="AH9">
-        <v>0.0009468527438145813</v>
+        <v>0</v>
       </c>
       <c r="AI9">
-        <v>0.000880719892781926</v>
+        <v>0</v>
       </c>
       <c r="AJ9">
-        <v>-0.32807968040278</v>
+        <v>-0.3146374829001368</v>
       </c>
       <c r="AK9">
-        <v>-0.2983032293377121</v>
+        <v>-0.2457264957264957</v>
       </c>
       <c r="AL9">
-        <v>0</v>
+        <v>0.067</v>
       </c>
       <c r="AM9">
-        <v>-7.62</v>
+        <v>-0.134</v>
       </c>
       <c r="AN9">
-        <v>0.04181818181818182</v>
+        <v>0</v>
+      </c>
+      <c r="AO9">
+        <v>106.2686567164179</v>
       </c>
       <c r="AP9">
-        <v>-10.9</v>
+        <v>-3.010471204188482</v>
       </c>
       <c r="AQ9">
-        <v>-3.412073490813648</v>
+        <v>-53.13432835820895</v>
       </c>
     </row>
     <row r="10">
@@ -1609,7 +1573,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ASTMAX Co., Ltd. (TSE:7162)</t>
+          <t>First Brothers Co.,Ltd. (TSE:3454)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1618,46 +1582,46 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.285</v>
+        <v>-0.0443</v>
       </c>
       <c r="E10">
-        <v>-0.162</v>
+        <v>0.0192</v>
       </c>
       <c r="G10">
-        <v>0.06701030927835051</v>
+        <v>0.156203288490284</v>
       </c>
       <c r="H10">
-        <v>0.06701030927835051</v>
+        <v>0.156203288490284</v>
       </c>
       <c r="I10">
-        <v>0.01536169987017111</v>
+        <v>0.200872696788613</v>
       </c>
       <c r="J10">
-        <v>0.010305950545811</v>
+        <v>0.1491175962637177</v>
       </c>
       <c r="K10">
-        <v>2.58</v>
+        <v>20.9</v>
       </c>
       <c r="L10">
-        <v>0.0265979381443299</v>
+        <v>0.156203288490284</v>
       </c>
       <c r="M10">
-        <v>0.2709</v>
+        <v>2.884</v>
       </c>
       <c r="N10">
-        <v>0.01157692307692308</v>
+        <v>0.02849802371541502</v>
       </c>
       <c r="O10">
-        <v>0.105</v>
+        <v>0.1379904306220096</v>
       </c>
       <c r="P10">
-        <v>0.2709</v>
+        <v>2.884</v>
       </c>
       <c r="Q10">
-        <v>0.01157692307692308</v>
+        <v>0.02849802371541502</v>
       </c>
       <c r="R10">
-        <v>0.105</v>
+        <v>0.1379904306220096</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -1666,73 +1630,73 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>28.2</v>
+        <v>45.3</v>
       </c>
       <c r="V10">
-        <v>1.205128205128205</v>
+        <v>0.4476284584980237</v>
       </c>
       <c r="W10">
-        <v>0.05341614906832299</v>
+        <v>0.136959370904325</v>
       </c>
       <c r="X10">
-        <v>0.112090276102194</v>
+        <v>0.1519684161230773</v>
       </c>
       <c r="Y10">
-        <v>-0.05867412703387104</v>
+        <v>-0.01500904521875229</v>
       </c>
       <c r="Z10">
-        <v>1.711978938003194</v>
+        <v>0.2617083351512484</v>
       </c>
       <c r="AA10">
-        <v>0.01764357027053095</v>
+        <v>0.03902531785993357</v>
       </c>
       <c r="AB10">
-        <v>0.07971414274583008</v>
+        <v>0.05865867548467295</v>
       </c>
       <c r="AC10">
-        <v>-0.06207057247529913</v>
+        <v>-0.01963335762473938</v>
       </c>
       <c r="AD10">
-        <v>22.8</v>
+        <v>425.1</v>
       </c>
       <c r="AE10">
-        <v>1.759575562967014</v>
+        <v>2.616165848417928</v>
       </c>
       <c r="AF10">
-        <v>24.55957556296702</v>
+        <v>427.716165848418</v>
       </c>
       <c r="AG10">
-        <v>-3.640424437032983</v>
+        <v>382.416165848418</v>
       </c>
       <c r="AH10">
-        <v>0.5120890932556793</v>
+        <v>0.8086653300950477</v>
       </c>
       <c r="AI10">
-        <v>0.3613850639813322</v>
+        <v>0.7227179494754947</v>
       </c>
       <c r="AJ10">
-        <v>-0.184235963238795</v>
+        <v>0.7907431406424086</v>
       </c>
       <c r="AK10">
-        <v>-0.09156094816122129</v>
+        <v>0.6997344081391458</v>
       </c>
       <c r="AL10">
-        <v>0.394</v>
+        <v>4.28</v>
       </c>
       <c r="AM10">
-        <v>0.394</v>
+        <v>4.266</v>
       </c>
       <c r="AN10">
-        <v>6.209150326797386</v>
+        <v>11.71074380165289</v>
       </c>
       <c r="AO10">
-        <v>3.426395939086294</v>
+        <v>6.144859813084112</v>
       </c>
       <c r="AP10">
-        <v>-0.9914009904773919</v>
+        <v>10.53488060188479</v>
       </c>
       <c r="AQ10">
-        <v>3.426395939086294</v>
+        <v>6.16502578527895</v>
       </c>
     </row>
     <row r="11">
@@ -1752,28 +1716,25 @@
         </is>
       </c>
       <c r="D11">
-        <v>-0.159</v>
-      </c>
-      <c r="E11">
-        <v>-0.281</v>
+        <v>-0.0188</v>
       </c>
       <c r="G11">
-        <v>-0.0719298245614035</v>
+        <v>0.01837037037037037</v>
       </c>
       <c r="H11">
-        <v>-0.0719298245614035</v>
+        <v>0.01837037037037037</v>
       </c>
       <c r="I11">
-        <v>-0.09473684210526316</v>
+        <v>0.06444444444444444</v>
       </c>
       <c r="J11">
-        <v>-0.09431444854173651</v>
+        <v>0.04542701525054466</v>
       </c>
       <c r="K11">
-        <v>-0.007</v>
+        <v>-1.12</v>
       </c>
       <c r="L11">
-        <v>-0.0003070175438596491</v>
+        <v>-0.04148148148148149</v>
       </c>
       <c r="M11">
         <v>-0</v>
@@ -1797,73 +1758,73 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>26.7</v>
+        <v>20.7</v>
       </c>
       <c r="V11">
-        <v>0.8870431893687707</v>
+        <v>0.6592356687898089</v>
       </c>
       <c r="W11">
-        <v>-0.0001168614357262104</v>
+        <v>-0.02271805273833672</v>
       </c>
       <c r="X11">
-        <v>0.1458531210273985</v>
+        <v>0.107067951383914</v>
       </c>
       <c r="Y11">
-        <v>-0.1459699824631247</v>
+        <v>-0.1297860041222507</v>
       </c>
       <c r="Z11">
-        <v>0.1609033168666196</v>
+        <v>0.3110599078341014</v>
       </c>
       <c r="AA11">
-        <v>-0.01517550759881152</v>
+        <v>0.01413052317701274</v>
       </c>
       <c r="AB11">
-        <v>0.07982415028931596</v>
+        <v>0.06293078569162514</v>
       </c>
       <c r="AC11">
-        <v>-0.09499965788812748</v>
+        <v>-0.04880026251461239</v>
       </c>
       <c r="AD11">
-        <v>64.2</v>
+        <v>62.1</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>64.2</v>
+        <v>62.1</v>
       </c>
       <c r="AG11">
-        <v>37.5</v>
+        <v>41.40000000000001</v>
       </c>
       <c r="AH11">
-        <v>0.6808059384941675</v>
+        <v>0.6641711229946524</v>
       </c>
       <c r="AI11">
-        <v>0.5408593091828138</v>
+        <v>0.5490716180371353</v>
       </c>
       <c r="AJ11">
-        <v>0.5547337278106509</v>
+        <v>0.5686813186813187</v>
       </c>
       <c r="AK11">
-        <v>0.4076086956521739</v>
+        <v>0.4480519480519481</v>
       </c>
       <c r="AL11">
-        <v>1.53</v>
+        <v>1.21</v>
       </c>
       <c r="AM11">
-        <v>1.489</v>
+        <v>1.17</v>
       </c>
       <c r="AN11">
-        <v>-36.47727272727273</v>
+        <v>29.85576923076923</v>
       </c>
       <c r="AO11">
-        <v>-1.411764705882353</v>
+        <v>1.43801652892562</v>
       </c>
       <c r="AP11">
-        <v>-21.30681818181818</v>
+        <v>19.90384615384616</v>
       </c>
       <c r="AQ11">
-        <v>-1.45063801208865</v>
+        <v>1.487179487179487</v>
       </c>
     </row>
     <row r="12">
@@ -1874,7 +1835,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Asia Development Capital Co. Ltd. (TSE:9318)</t>
+          <t>ASTMAX Co., Ltd. (TSE:7162)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1883,115 +1844,118 @@
         </is>
       </c>
       <c r="D12">
-        <v>-0.139</v>
+        <v>0.07400000000000001</v>
       </c>
       <c r="G12">
-        <v>0.17825311942959</v>
+        <v>-0.04063205417607224</v>
       </c>
       <c r="H12">
-        <v>0.17825311942959</v>
+        <v>-0.04063205417607224</v>
       </c>
       <c r="I12">
-        <v>-0.3244206773618538</v>
+        <v>-0.0007027084776590269</v>
       </c>
       <c r="J12">
-        <v>-0.3244206773618538</v>
+        <v>-0.0007027084776590269</v>
       </c>
       <c r="K12">
-        <v>-16.6</v>
+        <v>-1.88</v>
       </c>
       <c r="L12">
-        <v>-2.959001782531194</v>
+        <v>-0.02121896162528217</v>
       </c>
       <c r="M12">
-        <v>-0</v>
+        <v>0.6063000000000001</v>
       </c>
       <c r="N12">
-        <v>-0</v>
+        <v>0.0282</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>-0.3225000000000001</v>
       </c>
       <c r="P12">
-        <v>-0</v>
+        <v>0.6063000000000001</v>
       </c>
       <c r="Q12">
-        <v>-0</v>
+        <v>0.0282</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>-0.3225000000000001</v>
       </c>
       <c r="S12">
         <v>0</v>
       </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
       <c r="U12">
-        <v>8.81</v>
+        <v>24.7</v>
       </c>
       <c r="V12">
-        <v>0.2481690140845071</v>
+        <v>1.148837209302326</v>
       </c>
       <c r="W12">
-        <v>-0.4547945205479452</v>
+        <v>-0.04759493670886076</v>
       </c>
       <c r="X12">
-        <v>0.07938024802941726</v>
+        <v>0.09777690281883489</v>
       </c>
       <c r="Y12">
-        <v>-0.5341747685773625</v>
+        <v>-0.1453718395276956</v>
       </c>
       <c r="Z12">
-        <v>0.1352785145888594</v>
+        <v>2.459997288872437</v>
       </c>
       <c r="AA12">
-        <v>-0.0438871473354232</v>
+        <v>-0.001728660949908884</v>
       </c>
       <c r="AB12">
-        <v>0.07938024802941726</v>
+        <v>0.0609387294183429</v>
       </c>
       <c r="AC12">
-        <v>-0.1232673953648405</v>
+        <v>-0.06266739036825178</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>30.6</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.916299855602949</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>32.51629985560295</v>
       </c>
       <c r="AG12">
-        <v>-8.81</v>
+        <v>7.816299855602953</v>
       </c>
       <c r="AH12">
-        <v>0</v>
+        <v>0.6019719962775297</v>
       </c>
       <c r="AI12">
-        <v>0</v>
+        <v>0.4508869689752483</v>
       </c>
       <c r="AJ12">
-        <v>-0.3300861745972275</v>
+        <v>0.2666195902655531</v>
       </c>
       <c r="AK12">
-        <v>-2.324538258575199</v>
+        <v>0.1648441544238155</v>
       </c>
       <c r="AL12">
-        <v>0.014</v>
+        <v>0.362</v>
       </c>
       <c r="AM12">
-        <v>-0.076</v>
+        <v>0.347</v>
       </c>
       <c r="AN12">
-        <v>-0</v>
+        <v>14.15356151711378</v>
       </c>
       <c r="AO12">
-        <v>-130</v>
+        <v>-0.3342541436464088</v>
       </c>
       <c r="AP12">
-        <v>5.438271604938271</v>
+        <v>3.615309831453725</v>
       </c>
       <c r="AQ12">
-        <v>23.94736842105263</v>
+        <v>-0.3487031700288185</v>
       </c>
     </row>
     <row r="13">
@@ -2002,7 +1966,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sun Capital Management Corp. (TSE:2134)</t>
+          <t>JAFCO Group Co., Ltd. (TSE:8595)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2011,112 +1975,121 @@
         </is>
       </c>
       <c r="D13">
-        <v>-0.0759</v>
+        <v>-0.08839999999999999</v>
+      </c>
+      <c r="E13">
+        <v>0.323</v>
       </c>
       <c r="G13">
-        <v>-1.329931972789116</v>
+        <v>-0.216076058772688</v>
       </c>
       <c r="H13">
-        <v>-1.329931972789116</v>
+        <v>-0.216076058772688</v>
       </c>
       <c r="I13">
-        <v>-1.438775510204082</v>
+        <v>-0.1037165082108902</v>
       </c>
       <c r="J13">
-        <v>-1.438775510204082</v>
+        <v>-0.06953269730677512</v>
       </c>
       <c r="K13">
-        <v>-10.3</v>
+        <v>280.5</v>
       </c>
       <c r="L13">
-        <v>-3.503401360544218</v>
+        <v>2.424373379429559</v>
       </c>
       <c r="M13">
-        <v>-0</v>
+        <v>336.4</v>
       </c>
       <c r="N13">
-        <v>-0</v>
+        <v>0.5275207777952015</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>1.199286987522282</v>
       </c>
       <c r="P13">
-        <v>-0</v>
+        <v>54.5</v>
       </c>
       <c r="Q13">
-        <v>-0</v>
+        <v>0.08546338403638074</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>0.1942959001782531</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>281.9</v>
+      </c>
+      <c r="T13">
+        <v>0.8379904875148633</v>
       </c>
       <c r="U13">
-        <v>0.373</v>
+        <v>380.5</v>
       </c>
       <c r="V13">
-        <v>0.02702898550724638</v>
+        <v>0.5966755527677591</v>
       </c>
       <c r="W13">
-        <v>-0.7463768115942029</v>
+        <v>0.2150084317032041</v>
       </c>
       <c r="X13">
-        <v>0.0883685965320722</v>
+        <v>0.0707509352784548</v>
       </c>
       <c r="Y13">
-        <v>-0.8347454081262751</v>
+        <v>0.1442574964247492</v>
       </c>
       <c r="Z13">
-        <v>0.2254601226993865</v>
+        <v>0.1151415634174255</v>
       </c>
       <c r="AA13">
-        <v>-0.3243865030674846</v>
+        <v>-0.008006103476532698</v>
       </c>
       <c r="AB13">
-        <v>0.07952620180573111</v>
+        <v>0.06606702913731462</v>
       </c>
       <c r="AC13">
-        <v>-0.4039127048732157</v>
+        <v>-0.07407313261384732</v>
       </c>
       <c r="AD13">
-        <v>3.98</v>
+        <v>101.3</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>3.98</v>
+        <v>101.3</v>
       </c>
       <c r="AG13">
-        <v>3.607</v>
+        <v>-279.2</v>
       </c>
       <c r="AH13">
-        <v>0.2238470191226097</v>
+        <v>0.1370771312584574</v>
       </c>
       <c r="AI13">
-        <v>0.4585253456221198</v>
+        <v>0.1042395554640873</v>
       </c>
       <c r="AJ13">
-        <v>0.2072154880220601</v>
+        <v>-0.7788005578800556</v>
       </c>
       <c r="AK13">
-        <v>0.4342121102684483</v>
+        <v>-0.4721799424995772</v>
       </c>
       <c r="AL13">
-        <v>0.062</v>
+        <v>0.623</v>
       </c>
       <c r="AM13">
-        <v>0</v>
+        <v>-5.507</v>
       </c>
       <c r="AN13">
-        <v>-1.14367816091954</v>
+        <v>-9.556603773584905</v>
       </c>
       <c r="AO13">
-        <v>-68.22580645161291</v>
+        <v>-19.26163723916533</v>
       </c>
       <c r="AP13">
-        <v>-1.036494252873563</v>
+        <v>26.33962264150943</v>
+      </c>
+      <c r="AQ13">
+        <v>2.179044852006537</v>
       </c>
     </row>
     <row r="14">
@@ -2127,72 +2100,328 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>Future Venture Capital Co., Ltd. (TSE:8462)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D14">
+        <v>-0.0216</v>
+      </c>
+      <c r="G14">
+        <v>0.1186246418338109</v>
+      </c>
+      <c r="H14">
+        <v>0.1186246418338109</v>
+      </c>
+      <c r="I14">
+        <v>-0.01719197707736389</v>
+      </c>
+      <c r="J14">
+        <v>-0.01719197707736389</v>
+      </c>
+      <c r="K14">
+        <v>12.5</v>
+      </c>
+      <c r="L14">
+        <v>3.581661891117478</v>
+      </c>
+      <c r="M14">
+        <v>0.663</v>
+      </c>
+      <c r="N14">
+        <v>0.02091482649842271</v>
+      </c>
+      <c r="O14">
+        <v>0.05304</v>
+      </c>
+      <c r="P14">
+        <v>-0</v>
+      </c>
+      <c r="Q14">
+        <v>-0</v>
+      </c>
+      <c r="R14">
+        <v>-0</v>
+      </c>
+      <c r="S14">
+        <v>0.663</v>
+      </c>
+      <c r="T14">
+        <v>1</v>
+      </c>
+      <c r="U14">
+        <v>31.4</v>
+      </c>
+      <c r="V14">
+        <v>0.9905362776025236</v>
+      </c>
+      <c r="W14">
+        <v>0.5924170616113744</v>
+      </c>
+      <c r="X14">
+        <v>0.06757914008240185</v>
+      </c>
+      <c r="Y14">
+        <v>0.5248379215289726</v>
+      </c>
+      <c r="Z14">
+        <v>0.8948717948717945</v>
+      </c>
+      <c r="AA14">
+        <v>-0.01538461538461538</v>
+      </c>
+      <c r="AB14">
+        <v>0.06757914008240185</v>
+      </c>
+      <c r="AC14">
+        <v>-0.08296375546701722</v>
+      </c>
+      <c r="AD14">
+        <v>0</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>0</v>
+      </c>
+      <c r="AG14">
+        <v>-31.4</v>
+      </c>
+      <c r="AH14">
+        <v>0</v>
+      </c>
+      <c r="AI14">
+        <v>0</v>
+      </c>
+      <c r="AJ14">
+        <v>-104.6666666666664</v>
+      </c>
+      <c r="AK14">
+        <v>-313.9999999999955</v>
+      </c>
+      <c r="AL14">
+        <v>0</v>
+      </c>
+      <c r="AM14">
+        <v>-0.321</v>
+      </c>
+      <c r="AN14">
+        <v>-0</v>
+      </c>
+      <c r="AP14">
+        <v>668.0851063829787</v>
+      </c>
+      <c r="AQ14">
+        <v>0.1869158878504673</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Sun Capital Management Corp. (TSE:2134)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D15">
+        <v>-0.03700000000000001</v>
+      </c>
+      <c r="G15">
+        <v>-1.36283185840708</v>
+      </c>
+      <c r="H15">
+        <v>-1.36283185840708</v>
+      </c>
+      <c r="I15">
+        <v>-1.199115044247788</v>
+      </c>
+      <c r="J15">
+        <v>-1.199115044247788</v>
+      </c>
+      <c r="K15">
+        <v>-4.02</v>
+      </c>
+      <c r="L15">
+        <v>-1.778761061946903</v>
+      </c>
+      <c r="M15">
+        <v>-0</v>
+      </c>
+      <c r="N15">
+        <v>-0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>-0</v>
+      </c>
+      <c r="Q15">
+        <v>-0</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>0.522</v>
+      </c>
+      <c r="V15">
+        <v>0.032625</v>
+      </c>
+      <c r="W15">
+        <v>-0.8645161290322579</v>
+      </c>
+      <c r="X15">
+        <v>0.06988782068677468</v>
+      </c>
+      <c r="Y15">
+        <v>-0.9344039497190326</v>
+      </c>
+      <c r="Z15">
+        <v>0.2846706134273837</v>
+      </c>
+      <c r="AA15">
+        <v>-0.3413528152160221</v>
+      </c>
+      <c r="AB15">
+        <v>0.06704569980197624</v>
+      </c>
+      <c r="AC15">
+        <v>-0.4083985150179983</v>
+      </c>
+      <c r="AD15">
+        <v>1.85</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <v>1.85</v>
+      </c>
+      <c r="AG15">
+        <v>1.328</v>
+      </c>
+      <c r="AH15">
+        <v>0.103641456582633</v>
+      </c>
+      <c r="AI15">
+        <v>0.3394495412844037</v>
+      </c>
+      <c r="AJ15">
+        <v>0.07663896583564174</v>
+      </c>
+      <c r="AK15">
+        <v>0.2694805194805195</v>
+      </c>
+      <c r="AL15">
+        <v>0.1</v>
+      </c>
+      <c r="AM15">
+        <v>0.08</v>
+      </c>
+      <c r="AN15">
+        <v>-0.7974137931034484</v>
+      </c>
+      <c r="AO15">
+        <v>-27.1</v>
+      </c>
+      <c r="AP15">
+        <v>-0.5724137931034483</v>
+      </c>
+      <c r="AQ15">
+        <v>-33.875</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
           <t>Perfect Solutions Group, Inc. (OTCPK:PSGI)</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="K14">
-        <v>-0.02</v>
-      </c>
-      <c r="M14">
-        <v>-0</v>
-      </c>
-      <c r="N14">
-        <v>-0</v>
-      </c>
-      <c r="O14">
-        <v>0</v>
-      </c>
-      <c r="P14">
-        <v>-0</v>
-      </c>
-      <c r="Q14">
-        <v>-0</v>
-      </c>
-      <c r="R14">
-        <v>0</v>
-      </c>
-      <c r="S14">
-        <v>0</v>
-      </c>
-      <c r="U14">
-        <v>0</v>
-      </c>
-      <c r="V14">
-        <v>0</v>
-      </c>
-      <c r="X14">
-        <v>0.07938024802941726</v>
-      </c>
-      <c r="AB14">
-        <v>0.07938024802941726</v>
-      </c>
-      <c r="AD14">
-        <v>0</v>
-      </c>
-      <c r="AE14">
-        <v>0</v>
-      </c>
-      <c r="AF14">
-        <v>0</v>
-      </c>
-      <c r="AG14">
-        <v>0</v>
-      </c>
-      <c r="AH14">
-        <v>0</v>
-      </c>
-      <c r="AJ14">
-        <v>0</v>
-      </c>
-      <c r="AL14">
-        <v>0</v>
-      </c>
-      <c r="AM14">
+      <c r="K16">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="M16">
+        <v>-0</v>
+      </c>
+      <c r="N16">
+        <v>-0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>-0</v>
+      </c>
+      <c r="Q16">
+        <v>-0</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>0</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <v>0.06757914008240185</v>
+      </c>
+      <c r="AB16">
+        <v>0.06757914008240185</v>
+      </c>
+      <c r="AD16">
+        <v>0</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>0</v>
+      </c>
+      <c r="AG16">
+        <v>0</v>
+      </c>
+      <c r="AH16">
+        <v>0</v>
+      </c>
+      <c r="AJ16">
+        <v>0</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
         <v>0</v>
       </c>
     </row>
